--- a/scouting_merged.xlsx
+++ b/scouting_merged.xlsx
@@ -1205,14 +1205,12 @@
       <c r="B11" s="3" t="n">
         <v>7221</v>
       </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
+      <c r="C11" s="3" t="n">
+        <v/>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Isaac</t>
+          <t>Tammy</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
@@ -1230,10 +1228,12 @@
         <v>0</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="3" t="n">
-        <v/>
+        <v>50</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
       </c>
       <c r="K11" s="3" t="n">
         <v/>
@@ -1242,7 +1242,7 @@
         <v>0</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>Dead on field</t>
+          <t>No shots made. Bot may have died on field</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>2026-04-10T15:31:36.419Z</t>
+          <t>2026-04-10T15:32:52.601Z</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>scouting_2026-04-10I.csv</t>
+          <t>scouting_2026-04-10 (1).csv</t>
         </is>
       </c>
     </row>
@@ -1272,12 +1272,14 @@
       <c r="B12" s="2" t="n">
         <v>7221</v>
       </c>
-      <c r="C12" s="2" t="n">
-        <v/>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Tammy</t>
+          <t>Isaac</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
@@ -1295,12 +1297,10 @@
         <v>0</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v/>
       </c>
       <c r="K12" s="2" t="n">
         <v/>
@@ -1309,7 +1309,7 @@
         <v>0</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -1318,17 +1318,17 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>No shots made. Bot may have died on field</t>
+          <t>Dead on field</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2026-04-10T15:32:52.601Z</t>
+          <t>2026-04-10T15:31:36.419Z</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>scouting_2026-04-10 (1).csv</t>
+          <t>scouting_2026-04-10I.csv</t>
         </is>
       </c>
     </row>
@@ -3197,10 +3197,8 @@
       <c r="B15" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
+      <c r="C15" s="3" t="n">
+        <v/>
       </c>
       <c r="D15" s="3" t="n">
         <v>0</v>
@@ -3217,10 +3215,12 @@
         <v>0</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="3" t="n">
-        <v/>
+        <v>50</v>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
       </c>
       <c r="J15" s="3" t="n">
         <v/>
@@ -3229,7 +3229,7 @@
         <v>0</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>Dead on field</t>
+          <t>No shots made. Bot may have died on field</t>
         </is>
       </c>
     </row>
@@ -3249,8 +3249,10 @@
       <c r="B16" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C16" s="2" t="n">
-        <v/>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
       </c>
       <c r="D16" s="2" t="n">
         <v>0</v>
@@ -3267,12 +3269,10 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v/>
       </c>
       <c r="J16" s="2" t="n">
         <v/>
@@ -3281,7 +3281,7 @@
         <v>0</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>No shots made. Bot may have died on field</t>
+          <t>Dead on field</t>
         </is>
       </c>
     </row>

--- a/scouting_merged.xlsx
+++ b/scouting_merged.xlsx
@@ -1205,12 +1205,14 @@
       <c r="B11" s="3" t="n">
         <v>7221</v>
       </c>
-      <c r="C11" s="3" t="n">
-        <v/>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Tammy</t>
+          <t>Isaac</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
@@ -1228,12 +1230,10 @@
         <v>0</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v/>
       </c>
       <c r="K11" s="3" t="n">
         <v/>
@@ -1242,7 +1242,7 @@
         <v>0</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>No shots made. Bot may have died on field</t>
+          <t>Dead on field</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>2026-04-10T15:32:52.601Z</t>
+          <t>2026-04-10T15:31:36.419Z</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>scouting_2026-04-10 (1).csv</t>
+          <t>scouting_2026-04-10I.csv</t>
         </is>
       </c>
     </row>
@@ -1272,14 +1272,12 @@
       <c r="B12" s="2" t="n">
         <v>7221</v>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
+      <c r="C12" s="2" t="n">
+        <v/>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Isaac</t>
+          <t>Tammy</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
@@ -1297,10 +1295,12 @@
         <v>0</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="2" t="n">
-        <v/>
+        <v>50</v>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
       </c>
       <c r="K12" s="2" t="n">
         <v/>
@@ -1309,7 +1309,7 @@
         <v>0</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -1318,17 +1318,17 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Dead on field</t>
+          <t>No shots made. Bot may have died on field</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2026-04-10T15:31:36.419Z</t>
+          <t>2026-04-10T15:32:52.601Z</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>scouting_2026-04-10I.csv</t>
+          <t>scouting_2026-04-10 (1).csv</t>
         </is>
       </c>
     </row>
@@ -3197,8 +3197,10 @@
       <c r="B15" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C15" s="3" t="n">
-        <v/>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
       </c>
       <c r="D15" s="3" t="n">
         <v>0</v>
@@ -3215,12 +3217,10 @@
         <v>0</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v/>
       </c>
       <c r="J15" s="3" t="n">
         <v/>
@@ -3229,7 +3229,7 @@
         <v>0</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>No shots made. Bot may have died on field</t>
+          <t>Dead on field</t>
         </is>
       </c>
     </row>
@@ -3249,10 +3249,8 @@
       <c r="B16" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
+      <c r="C16" s="2" t="n">
+        <v/>
       </c>
       <c r="D16" s="2" t="n">
         <v>0</v>
@@ -3269,10 +3267,12 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="2" t="n">
-        <v/>
+        <v>50</v>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
       </c>
       <c r="J16" s="2" t="n">
         <v/>
@@ -3281,7 +3281,7 @@
         <v>0</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Dead on field</t>
+          <t>No shots made. Bot may have died on field</t>
         </is>
       </c>
     </row>
